--- a/台北畫家管理費資訊-20241217.xlsx
+++ b/台北畫家管理費資訊-20241217.xlsx
@@ -833,6 +833,10 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
+    <t>劉諺璞</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
     <t>劉彥宏</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -841,14 +845,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>劉彥宏</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>劉諺璞</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>郭麗貞</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -870,6 +866,10 @@
   </si>
   <si>
     <t>2025/01/01</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>郭麗貞</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1815,7 +1815,7 @@
         <v>13</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>86</v>
@@ -1866,7 +1866,7 @@
     </row>
     <row r="17" spans="1:9">
       <c r="A17" s="2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>47</v>
@@ -1891,7 +1891,7 @@
         <v>500</v>
       </c>
       <c r="I17" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="18" spans="1:9">
@@ -2957,10 +2957,10 @@
       </c>
       <c r="B17" s="2"/>
       <c r="C17" s="11" t="s">
+        <v>233</v>
+      </c>
+      <c r="D17" s="11" t="s">
         <v>234</v>
-      </c>
-      <c r="D17" s="11" t="s">
-        <v>235</v>
       </c>
       <c r="E17" s="6">
         <v>0</v>
@@ -3246,7 +3246,7 @@
         <v>27</v>
       </c>
       <c r="B27" s="28" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C27" s="11" t="s">
         <v>215</v>
@@ -3277,7 +3277,7 @@
         <v>28</v>
       </c>
       <c r="B28" s="28" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C28" s="11" t="s">
         <v>215</v>
@@ -3453,7 +3453,7 @@
         <v>127</v>
       </c>
       <c r="B34" s="19" t="s">
-        <v>226</v>
+        <v>118</v>
       </c>
       <c r="C34" s="20" t="s">
         <v>70</v>
@@ -3484,7 +3484,7 @@
         <v>28</v>
       </c>
       <c r="B35" s="19" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C35" s="20" t="s">
         <v>70</v>
@@ -3515,7 +3515,7 @@
         <v>27</v>
       </c>
       <c r="B36" s="24" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="C36" s="25" t="s">
         <v>112</v>
@@ -3527,7 +3527,7 @@
         <v>0</v>
       </c>
       <c r="F36" s="26">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G36" s="22" t="s">
         <v>126</v>
@@ -3538,7 +3538,7 @@
       </c>
       <c r="I36" s="23">
         <f t="shared" si="1"/>
-        <v>11000</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="37" spans="1:9">
@@ -3546,7 +3546,7 @@
         <v>28</v>
       </c>
       <c r="B37" s="24" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C37" s="25" t="s">
         <v>112</v>
@@ -3577,7 +3577,7 @@
         <v>27</v>
       </c>
       <c r="B38" s="24" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C38" s="25" t="s">
         <v>128</v>
@@ -3589,7 +3589,7 @@
         <v>0</v>
       </c>
       <c r="F38" s="26">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G38" s="22" t="s">
         <v>126</v>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="I38" s="23">
         <f t="shared" ref="I38:I39" si="5">(H38*500)+(H38*E38*100)+(H38*F38*50)</f>
-        <v>15400</v>
+        <v>14000</v>
       </c>
     </row>
     <row r="39" spans="1:9">
@@ -3608,7 +3608,7 @@
         <v>28</v>
       </c>
       <c r="B39" s="24" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C39" s="25" t="s">
         <v>128</v>
